--- a/datasets/day1_excel_foundations/homework/homework_answer_key.xlsx
+++ b/datasets/day1_excel_foundations/homework/homework_answer_key.xlsx
@@ -591,8 +591,8 @@
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2156,11 +2156,11 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Q7  Total sales outside the United States</t>
+          <t>Q7  Total sales outside Zimbabwe</t>
         </is>
       </c>
       <c r="B10" s="5">
-        <f>SUMIF('Branch Orders'!D2:D36,"&lt;&gt;United States",'Branch Orders'!H2:H36)</f>
+        <f>SUMIF('Branch Orders'!D2:D36,"&lt;&gt;Zimbabwe",'Branch Orders'!H2:H36)</f>
         <v/>
       </c>
     </row>
